--- a/data/trans_bre/P1401-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1401-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>46,93%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,29</t>
+          <t>-0,31; 2,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,4</t>
+          <t>-0,38; 2,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,75</t>
+          <t>-0,13; 2,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 192,05</t>
+          <t>-14,84; 192,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 199,37</t>
+          <t>-18,05; 202,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 128,28</t>
+          <t>-4,66; 135,02</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,54</t>
+          <t>-0,04; 1,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,24</t>
+          <t>0,08; 1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,77</t>
+          <t>-0,65; 0,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 221,45</t>
+          <t>-7,87; 221,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 300,16</t>
+          <t>4,56; 328,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,36; 67,32</t>
+          <t>-30,1; 54,57</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-42,88%</t>
+          <t>-44,65%</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,75</t>
+          <t>-0,45; 1,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,77</t>
+          <t>1,31; 4,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,17</t>
+          <t>-2,66; -0,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69,0; 2607,11</t>
+          <t>63,96; 2636,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,08; 16,24</t>
+          <t>-75,67; 2,77</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,51</t>
+          <t>0,22; 1,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,76</t>
+          <t>0,56; 1,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,79</t>
+          <t>-0,43; 0,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,73; 170,82</t>
+          <t>11,61; 164,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,7; 274,65</t>
+          <t>44,94; 269,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 48,33</t>
+          <t>-17,78; 43,37</t>
         </is>
       </c>
     </row>
